--- a/artfynd/A 15103-2025 artfynd.xlsx
+++ b/artfynd/A 15103-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -806,133 +806,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>117684724</v>
-      </c>
-      <c r="B3" t="n">
-        <v>106569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>219955</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Slåttergubbe</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Arnica montana</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Rydbo, Egaredsvägen, Hl</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>349663</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6343361</v>
-      </c>
-      <c r="S3" t="n">
-        <v>5</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Halland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Varberg</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Halland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Skällinge</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>N-Var-0827</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>3 blomstänglar</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Eva Eriksson</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Eva Eriksson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>
